--- a/output/yearly_population_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_41_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5493</v>
+        <v>4952</v>
       </c>
       <c r="C2" t="n">
-        <v>15015</v>
+        <v>17087</v>
       </c>
       <c r="D2" t="n">
-        <v>27937</v>
+        <v>31686</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3317</v>
+        <v>3068</v>
       </c>
       <c r="C3" t="n">
-        <v>6612</v>
+        <v>6728</v>
       </c>
       <c r="D3" t="n">
-        <v>11523</v>
+        <v>13277</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2782</v>
+        <v>2688</v>
       </c>
       <c r="C4" t="n">
-        <v>5076</v>
+        <v>6646</v>
       </c>
       <c r="D4" t="n">
-        <v>4496</v>
+        <v>5910</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1894</v>
+        <v>1688</v>
       </c>
       <c r="C5" t="n">
-        <v>4192</v>
+        <v>5901</v>
       </c>
       <c r="D5" t="n">
-        <v>1738</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1070</v>
+        <v>921</v>
       </c>
       <c r="C6" t="n">
-        <v>3502</v>
+        <v>4315</v>
       </c>
       <c r="D6" t="n">
-        <v>917</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>502</v>
+        <v>419</v>
       </c>
       <c r="C7" t="n">
-        <v>2342</v>
+        <v>2626</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>647</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="C8" t="n">
-        <v>1200</v>
+        <v>1137</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6379</v>
+        <v>6547</v>
       </c>
       <c r="C2" t="n">
-        <v>10728</v>
+        <v>10832</v>
       </c>
       <c r="D2" t="n">
-        <v>29934</v>
+        <v>36795</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3469</v>
+        <v>3139</v>
       </c>
       <c r="C3" t="n">
-        <v>9179</v>
+        <v>9847</v>
       </c>
       <c r="D3" t="n">
-        <v>12980</v>
+        <v>14762</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2580</v>
+        <v>2439</v>
       </c>
       <c r="C4" t="n">
-        <v>5707</v>
+        <v>6480</v>
       </c>
       <c r="D4" t="n">
-        <v>5506</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2015</v>
+        <v>1852</v>
       </c>
       <c r="C5" t="n">
-        <v>4471</v>
+        <v>6107</v>
       </c>
       <c r="D5" t="n">
-        <v>2092</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1305</v>
+        <v>1121</v>
       </c>
       <c r="C6" t="n">
-        <v>3779</v>
+        <v>4902</v>
       </c>
       <c r="D6" t="n">
-        <v>1030</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>662</v>
+        <v>561</v>
       </c>
       <c r="C7" t="n">
-        <v>2829</v>
+        <v>3310</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="C8" t="n">
-        <v>1691</v>
+        <v>1749</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C9" t="n">
-        <v>770</v>
+        <v>699</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7815</v>
+        <v>6459</v>
       </c>
       <c r="C2" t="n">
-        <v>16820</v>
+        <v>8378</v>
       </c>
       <c r="D2" t="n">
-        <v>24281</v>
+        <v>35624</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3771</v>
+        <v>3571</v>
       </c>
       <c r="C3" t="n">
-        <v>8708</v>
+        <v>9114</v>
       </c>
       <c r="D3" t="n">
-        <v>14183</v>
+        <v>16602</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2529</v>
+        <v>2307</v>
       </c>
       <c r="C4" t="n">
-        <v>7033</v>
+        <v>7735</v>
       </c>
       <c r="D4" t="n">
-        <v>6362</v>
+        <v>7602</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2001</v>
+        <v>1853</v>
       </c>
       <c r="C5" t="n">
-        <v>4900</v>
+        <v>6068</v>
       </c>
       <c r="D5" t="n">
-        <v>2520</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1447</v>
+        <v>1269</v>
       </c>
       <c r="C6" t="n">
-        <v>3987</v>
+        <v>5275</v>
       </c>
       <c r="D6" t="n">
-        <v>1149</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>819</v>
+        <v>689</v>
       </c>
       <c r="C7" t="n">
-        <v>3181</v>
+        <v>3917</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>377</v>
+        <v>308</v>
       </c>
       <c r="C8" t="n">
-        <v>2136</v>
+        <v>2297</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="C9" t="n">
-        <v>1105</v>
+        <v>1062</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>486</v>
+        <v>432</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7096</v>
+        <v>6025</v>
       </c>
       <c r="C2" t="n">
-        <v>11572</v>
+        <v>5898</v>
       </c>
       <c r="D2" t="n">
-        <v>20105</v>
+        <v>29455</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4532</v>
+        <v>4156</v>
       </c>
       <c r="C3" t="n">
-        <v>13146</v>
+        <v>12969</v>
       </c>
       <c r="D3" t="n">
-        <v>14889</v>
+        <v>17389</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1848</v>
+        <v>1712</v>
       </c>
       <c r="C4" t="n">
-        <v>8552</v>
+        <v>9835</v>
       </c>
       <c r="D4" t="n">
-        <v>5894</v>
+        <v>7164</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1337</v>
+        <v>1172</v>
       </c>
       <c r="C5" t="n">
-        <v>3907</v>
+        <v>5169</v>
       </c>
       <c r="D5" t="n">
-        <v>1803</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>756</v>
+        <v>636</v>
       </c>
       <c r="C6" t="n">
-        <v>3117</v>
+        <v>3838</v>
       </c>
       <c r="D6" t="n">
-        <v>682</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>348</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>2093</v>
+        <v>2251</v>
       </c>
       <c r="D7" t="n">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>1082</v>
+        <v>1040</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>476</v>
+        <v>423</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4324</v>
+        <v>3689</v>
       </c>
       <c r="C2" t="n">
-        <v>5401</v>
+        <v>3053</v>
       </c>
       <c r="D2" t="n">
-        <v>15348</v>
+        <v>21640</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4819</v>
+        <v>4239</v>
       </c>
       <c r="C3" t="n">
-        <v>11283</v>
+        <v>9035</v>
       </c>
       <c r="D3" t="n">
-        <v>14883</v>
+        <v>17959</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2493</v>
+        <v>2256</v>
       </c>
       <c r="C4" t="n">
-        <v>10819</v>
+        <v>11392</v>
       </c>
       <c r="D4" t="n">
-        <v>7066</v>
+        <v>8556</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1468</v>
+        <v>1288</v>
       </c>
       <c r="C5" t="n">
-        <v>5886</v>
+        <v>7051</v>
       </c>
       <c r="D5" t="n">
-        <v>2293</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>897</v>
+        <v>751</v>
       </c>
       <c r="C6" t="n">
-        <v>3542</v>
+        <v>4508</v>
       </c>
       <c r="D6" t="n">
-        <v>801</v>
+        <v>890</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>2547</v>
+        <v>2815</v>
       </c>
       <c r="D7" t="n">
-        <v>502</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>1394</v>
+        <v>1377</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>527</v>
+        <v>450</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4298</v>
+        <v>4303</v>
       </c>
       <c r="C2" t="n">
-        <v>5112</v>
+        <v>4914</v>
       </c>
       <c r="D2" t="n">
-        <v>12899</v>
+        <v>18142</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3875</v>
+        <v>3383</v>
       </c>
       <c r="C3" t="n">
-        <v>7619</v>
+        <v>5620</v>
       </c>
       <c r="D3" t="n">
-        <v>13946</v>
+        <v>17425</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3000</v>
+        <v>2619</v>
       </c>
       <c r="C4" t="n">
-        <v>10816</v>
+        <v>10155</v>
       </c>
       <c r="D4" t="n">
-        <v>8126</v>
+        <v>9740</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>1496</v>
       </c>
       <c r="C5" t="n">
-        <v>8036</v>
+        <v>8821</v>
       </c>
       <c r="D5" t="n">
-        <v>2956</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1038</v>
+        <v>883</v>
       </c>
       <c r="C6" t="n">
-        <v>4577</v>
+        <v>5540</v>
       </c>
       <c r="D6" t="n">
-        <v>1005</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>481</v>
+        <v>392</v>
       </c>
       <c r="C7" t="n">
-        <v>2965</v>
+        <v>3538</v>
       </c>
       <c r="D7" t="n">
-        <v>537</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>1870</v>
+        <v>1939</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>859</v>
+        <v>781</v>
       </c>
       <c r="D9" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2589</v>
+        <v>2585</v>
       </c>
       <c r="C2" t="n">
-        <v>2453</v>
+        <v>2442</v>
       </c>
       <c r="D2" t="n">
-        <v>9017</v>
+        <v>12847</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3835</v>
+        <v>3494</v>
       </c>
       <c r="C3" t="n">
-        <v>6577</v>
+        <v>5255</v>
       </c>
       <c r="D3" t="n">
-        <v>13524</v>
+        <v>17131</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3312</v>
+        <v>2852</v>
       </c>
       <c r="C4" t="n">
-        <v>10616</v>
+        <v>9569</v>
       </c>
       <c r="D4" t="n">
-        <v>8800</v>
+        <v>10569</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1778</v>
+        <v>1551</v>
       </c>
       <c r="C5" t="n">
-        <v>9855</v>
+        <v>10500</v>
       </c>
       <c r="D5" t="n">
-        <v>3151</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>856</v>
+        <v>704</v>
       </c>
       <c r="C6" t="n">
-        <v>5483</v>
+        <v>6462</v>
       </c>
       <c r="D6" t="n">
-        <v>1008</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>3229</v>
+        <v>3602</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>1391</v>
+        <v>1316</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3467</v>
+        <v>2534</v>
       </c>
       <c r="C2" t="n">
-        <v>5692</v>
+        <v>11076</v>
       </c>
       <c r="D2" t="n">
-        <v>10917</v>
+        <v>14867</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2854</v>
+        <v>2681</v>
       </c>
       <c r="C3" t="n">
-        <v>4244</v>
+        <v>3611</v>
       </c>
       <c r="D3" t="n">
-        <v>12132</v>
+        <v>15458</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3075</v>
+        <v>2705</v>
       </c>
       <c r="C4" t="n">
-        <v>8534</v>
+        <v>7515</v>
       </c>
       <c r="D4" t="n">
-        <v>9258</v>
+        <v>11255</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2121</v>
+        <v>1829</v>
       </c>
       <c r="C5" t="n">
-        <v>10080</v>
+        <v>9888</v>
       </c>
       <c r="D5" t="n">
-        <v>3868</v>
+        <v>4555</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1094</v>
+        <v>917</v>
       </c>
       <c r="C6" t="n">
-        <v>7292</v>
+        <v>8159</v>
       </c>
       <c r="D6" t="n">
-        <v>1282</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
-        <v>4174</v>
+        <v>4700</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>2066</v>
+        <v>2125</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>673</v>
+        <v>615</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" t="n">
         <v>59</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2446</v>
+        <v>1791</v>
       </c>
       <c r="C2" t="n">
-        <v>3250</v>
+        <v>6632</v>
       </c>
       <c r="D2" t="n">
-        <v>8618</v>
+        <v>10993</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2669</v>
+        <v>2313</v>
       </c>
       <c r="C3" t="n">
-        <v>4407</v>
+        <v>5801</v>
       </c>
       <c r="D3" t="n">
-        <v>11442</v>
+        <v>14575</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2748</v>
+        <v>2483</v>
       </c>
       <c r="C4" t="n">
-        <v>6913</v>
+        <v>6075</v>
       </c>
       <c r="D4" t="n">
-        <v>9424</v>
+        <v>11545</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2301</v>
+        <v>1965</v>
       </c>
       <c r="C5" t="n">
-        <v>9626</v>
+        <v>9264</v>
       </c>
       <c r="D5" t="n">
-        <v>4393</v>
+        <v>5211</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1272</v>
+        <v>1056</v>
       </c>
       <c r="C6" t="n">
-        <v>8430</v>
+        <v>8989</v>
       </c>
       <c r="D6" t="n">
-        <v>1490</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>224</v>
       </c>
       <c r="C7" t="n">
-        <v>5192</v>
+        <v>5720</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>691</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>2596</v>
+        <v>2727</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>753</v>
+        <v>652</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3691</v>
+        <v>2830</v>
       </c>
       <c r="C2" t="n">
-        <v>12240</v>
+        <v>7500</v>
       </c>
       <c r="D2" t="n">
-        <v>12669</v>
+        <v>11880</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2182</v>
+        <v>1802</v>
       </c>
       <c r="C3" t="n">
-        <v>3529</v>
+        <v>5514</v>
       </c>
       <c r="D3" t="n">
-        <v>10480</v>
+        <v>13264</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2387</v>
+        <v>2129</v>
       </c>
       <c r="C4" t="n">
-        <v>5734</v>
+        <v>5782</v>
       </c>
       <c r="D4" t="n">
-        <v>9318</v>
+        <v>11601</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2237</v>
+        <v>1944</v>
       </c>
       <c r="C5" t="n">
-        <v>8357</v>
+        <v>7846</v>
       </c>
       <c r="D5" t="n">
-        <v>4935</v>
+        <v>5843</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1495</v>
+        <v>1248</v>
       </c>
       <c r="C6" t="n">
-        <v>8808</v>
+        <v>9017</v>
       </c>
       <c r="D6" t="n">
-        <v>1833</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>515</v>
+        <v>413</v>
       </c>
       <c r="C7" t="n">
-        <v>6364</v>
+        <v>6927</v>
       </c>
       <c r="D7" t="n">
-        <v>750</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>3510</v>
+        <v>3693</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1338</v>
+        <v>1288</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>383</v>
+        <v>338</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5888</v>
+        <v>5024</v>
       </c>
       <c r="C2" t="n">
-        <v>11892</v>
+        <v>9822</v>
       </c>
       <c r="D2" t="n">
-        <v>4153</v>
+        <v>11612</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2668</v>
+        <v>2089</v>
       </c>
       <c r="C2" t="n">
-        <v>7148</v>
+        <v>4440</v>
       </c>
       <c r="D2" t="n">
-        <v>9425</v>
+        <v>8838</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2947</v>
+        <v>2441</v>
       </c>
       <c r="C3" t="n">
-        <v>5726</v>
+        <v>6540</v>
       </c>
       <c r="D3" t="n">
-        <v>11396</v>
+        <v>14289</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3266</v>
+        <v>2866</v>
       </c>
       <c r="C4" t="n">
-        <v>8537</v>
+        <v>8499</v>
       </c>
       <c r="D4" t="n">
-        <v>9503</v>
+        <v>11704</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1422</v>
+        <v>1171</v>
       </c>
       <c r="C5" t="n">
-        <v>12373</v>
+        <v>12230</v>
       </c>
       <c r="D5" t="n">
-        <v>4469</v>
+        <v>5174</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>475</v>
+        <v>381</v>
       </c>
       <c r="C6" t="n">
-        <v>7790</v>
+        <v>8290</v>
       </c>
       <c r="D6" t="n">
-        <v>1519</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>3439</v>
+        <v>3619</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1311</v>
+        <v>1262</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6874</v>
+        <v>6003</v>
       </c>
       <c r="C2" t="n">
-        <v>6645</v>
+        <v>9147</v>
       </c>
       <c r="D2" t="n">
-        <v>7233</v>
+        <v>13760</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2502</v>
+        <v>2135</v>
       </c>
       <c r="C3" t="n">
-        <v>5993</v>
+        <v>4950</v>
       </c>
       <c r="D3" t="n">
-        <v>1337</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5000</v>
+        <v>4357</v>
       </c>
       <c r="C2" t="n">
-        <v>6669</v>
+        <v>9962</v>
       </c>
       <c r="D2" t="n">
-        <v>9920</v>
+        <v>18388</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3849</v>
+        <v>3340</v>
       </c>
       <c r="C3" t="n">
-        <v>5486</v>
+        <v>6317</v>
       </c>
       <c r="D3" t="n">
-        <v>2229</v>
+        <v>4275</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1120</v>
+        <v>962</v>
       </c>
       <c r="C4" t="n">
-        <v>3553</v>
+        <v>2944</v>
       </c>
       <c r="D4" t="n">
-        <v>1450</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5877</v>
+        <v>5494</v>
       </c>
       <c r="C2" t="n">
-        <v>7828</v>
+        <v>11850</v>
       </c>
       <c r="D2" t="n">
-        <v>12779</v>
+        <v>15991</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3632</v>
+        <v>3159</v>
       </c>
       <c r="C3" t="n">
-        <v>5307</v>
+        <v>7249</v>
       </c>
       <c r="D3" t="n">
-        <v>3299</v>
+        <v>6225</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2112</v>
+        <v>1828</v>
       </c>
       <c r="C4" t="n">
-        <v>4573</v>
+        <v>4732</v>
       </c>
       <c r="D4" t="n">
-        <v>1555</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>510</v>
+        <v>447</v>
       </c>
       <c r="C5" t="n">
-        <v>2039</v>
+        <v>1705</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5524</v>
+        <v>5020</v>
       </c>
       <c r="C2" t="n">
-        <v>5758</v>
+        <v>6453</v>
       </c>
       <c r="D2" t="n">
-        <v>18413</v>
+        <v>16303</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3849</v>
+        <v>3475</v>
       </c>
       <c r="C3" t="n">
-        <v>5748</v>
+        <v>8345</v>
       </c>
       <c r="D3" t="n">
-        <v>4507</v>
+        <v>7271</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2444</v>
+        <v>2094</v>
       </c>
       <c r="C4" t="n">
-        <v>4872</v>
+        <v>5917</v>
       </c>
       <c r="D4" t="n">
-        <v>1825</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1073</v>
+        <v>936</v>
       </c>
       <c r="C5" t="n">
-        <v>3290</v>
+        <v>3238</v>
       </c>
       <c r="D5" t="n">
-        <v>1202</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>1181</v>
+        <v>1000</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6652</v>
+        <v>6837</v>
       </c>
       <c r="C2" t="n">
-        <v>5881</v>
+        <v>11492</v>
       </c>
       <c r="D2" t="n">
-        <v>19003</v>
+        <v>26903</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3392</v>
+        <v>3059</v>
       </c>
       <c r="C3" t="n">
-        <v>4713</v>
+        <v>6064</v>
       </c>
       <c r="D3" t="n">
-        <v>5929</v>
+        <v>7651</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1939</v>
+        <v>1703</v>
       </c>
       <c r="C4" t="n">
-        <v>4386</v>
+        <v>5872</v>
       </c>
       <c r="D4" t="n">
-        <v>1969</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>921</v>
+        <v>783</v>
       </c>
       <c r="C5" t="n">
-        <v>2976</v>
+        <v>3380</v>
       </c>
       <c r="D5" t="n">
-        <v>1022</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="C6" t="n">
-        <v>1512</v>
+        <v>1417</v>
       </c>
       <c r="D6" t="n">
-        <v>752</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>484</v>
+        <v>420</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5055</v>
+        <v>4920</v>
       </c>
       <c r="C2" t="n">
-        <v>8561</v>
+        <v>7973</v>
       </c>
       <c r="D2" t="n">
-        <v>24196</v>
+        <v>22688</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4178</v>
+        <v>4095</v>
       </c>
       <c r="C3" t="n">
-        <v>4685</v>
+        <v>7912</v>
       </c>
       <c r="D3" t="n">
-        <v>7689</v>
+        <v>10322</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2341</v>
+        <v>2080</v>
       </c>
       <c r="C4" t="n">
-        <v>4450</v>
+        <v>5864</v>
       </c>
       <c r="D4" t="n">
-        <v>2688</v>
+        <v>3918</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1268</v>
+        <v>1094</v>
       </c>
       <c r="C5" t="n">
-        <v>3753</v>
+        <v>4745</v>
       </c>
       <c r="D5" t="n">
-        <v>1181</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>578</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>2336</v>
+        <v>2479</v>
       </c>
       <c r="D6" t="n">
-        <v>785</v>
+        <v>856</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="C7" t="n">
-        <v>1068</v>
+        <v>976</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>131</v>
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4275</v>
+        <v>3699</v>
       </c>
       <c r="C2" t="n">
-        <v>9292</v>
+        <v>8531</v>
       </c>
       <c r="D2" t="n">
-        <v>26579</v>
+        <v>29481</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3796</v>
+        <v>3703</v>
       </c>
       <c r="C3" t="n">
-        <v>5884</v>
+        <v>6901</v>
       </c>
       <c r="D3" t="n">
-        <v>9776</v>
+        <v>11474</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2781</v>
+        <v>2631</v>
       </c>
       <c r="C4" t="n">
-        <v>4490</v>
+        <v>6806</v>
       </c>
       <c r="D4" t="n">
-        <v>3566</v>
+        <v>4929</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1590</v>
+        <v>1371</v>
       </c>
       <c r="C5" t="n">
-        <v>4056</v>
+        <v>5247</v>
       </c>
       <c r="D5" t="n">
-        <v>1408</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>832</v>
+        <v>714</v>
       </c>
       <c r="C6" t="n">
-        <v>3034</v>
+        <v>3625</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>723</v>
+        <v>642</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
         <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_41_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4952</v>
+        <v>8304</v>
       </c>
       <c r="C2" t="n">
-        <v>17087</v>
+        <v>7192</v>
       </c>
       <c r="D2" t="n">
-        <v>31686</v>
+        <v>45881</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3068</v>
+        <v>4173</v>
       </c>
       <c r="C3" t="n">
-        <v>6728</v>
+        <v>6200</v>
       </c>
       <c r="D3" t="n">
-        <v>13277</v>
+        <v>19012</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2688</v>
+        <v>3082</v>
       </c>
       <c r="C4" t="n">
-        <v>6646</v>
+        <v>5533</v>
       </c>
       <c r="D4" t="n">
-        <v>5910</v>
+        <v>8973</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>2122</v>
       </c>
       <c r="C5" t="n">
-        <v>5901</v>
+        <v>3749</v>
       </c>
       <c r="D5" t="n">
-        <v>2350</v>
+        <v>3354</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>921</v>
+        <v>1253</v>
       </c>
       <c r="C6" t="n">
-        <v>4315</v>
+        <v>2858</v>
       </c>
       <c r="D6" t="n">
-        <v>1103</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>419</v>
+        <v>598</v>
       </c>
       <c r="C7" t="n">
-        <v>2626</v>
+        <v>1733</v>
       </c>
       <c r="D7" t="n">
-        <v>647</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="C8" t="n">
-        <v>1137</v>
+        <v>816</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>425</v>
+        <v>351</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="D10" t="n">
         <v>245</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6547</v>
+        <v>8216</v>
       </c>
       <c r="C2" t="n">
-        <v>10832</v>
+        <v>7817</v>
       </c>
       <c r="D2" t="n">
-        <v>36795</v>
+        <v>50067</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3139</v>
+        <v>4790</v>
       </c>
       <c r="C3" t="n">
-        <v>9847</v>
+        <v>5856</v>
       </c>
       <c r="D3" t="n">
-        <v>14762</v>
+        <v>21204</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2439</v>
+        <v>3023</v>
       </c>
       <c r="C4" t="n">
-        <v>6480</v>
+        <v>5672</v>
       </c>
       <c r="D4" t="n">
-        <v>6805</v>
+        <v>10156</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1852</v>
+        <v>2239</v>
       </c>
       <c r="C5" t="n">
-        <v>6107</v>
+        <v>4475</v>
       </c>
       <c r="D5" t="n">
-        <v>2825</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1121</v>
+        <v>1486</v>
       </c>
       <c r="C6" t="n">
-        <v>4902</v>
+        <v>3188</v>
       </c>
       <c r="D6" t="n">
-        <v>1257</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>561</v>
+        <v>775</v>
       </c>
       <c r="C7" t="n">
-        <v>3310</v>
+        <v>2217</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>228</v>
+        <v>329</v>
       </c>
       <c r="C8" t="n">
-        <v>1749</v>
+        <v>1185</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C9" t="n">
-        <v>699</v>
+        <v>534</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="D10" t="n">
         <v>247</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6459</v>
+        <v>8922</v>
       </c>
       <c r="C2" t="n">
-        <v>8378</v>
+        <v>15372</v>
       </c>
       <c r="D2" t="n">
-        <v>35624</v>
+        <v>58888</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>5043</v>
       </c>
       <c r="C3" t="n">
-        <v>9114</v>
+        <v>5899</v>
       </c>
       <c r="D3" t="n">
-        <v>16602</v>
+        <v>23310</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2307</v>
+        <v>3143</v>
       </c>
       <c r="C4" t="n">
-        <v>7735</v>
+        <v>5631</v>
       </c>
       <c r="D4" t="n">
-        <v>7602</v>
+        <v>11438</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1853</v>
+        <v>2266</v>
       </c>
       <c r="C5" t="n">
-        <v>6068</v>
+        <v>4821</v>
       </c>
       <c r="D5" t="n">
-        <v>3246</v>
+        <v>4762</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1269</v>
+        <v>1623</v>
       </c>
       <c r="C6" t="n">
-        <v>5275</v>
+        <v>3635</v>
       </c>
       <c r="D6" t="n">
-        <v>1451</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>689</v>
+        <v>940</v>
       </c>
       <c r="C7" t="n">
-        <v>3917</v>
+        <v>2596</v>
       </c>
       <c r="D7" t="n">
-        <v>762</v>
+        <v>864</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>308</v>
+        <v>438</v>
       </c>
       <c r="C8" t="n">
-        <v>2297</v>
+        <v>1557</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C9" t="n">
-        <v>1062</v>
+        <v>764</v>
       </c>
       <c r="D9" t="n">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>432</v>
+        <v>355</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1542,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>150</v>
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6025</v>
+        <v>8307</v>
       </c>
       <c r="C2" t="n">
-        <v>5898</v>
+        <v>10698</v>
       </c>
       <c r="D2" t="n">
-        <v>29455</v>
+        <v>48229</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4156</v>
+        <v>5814</v>
       </c>
       <c r="C3" t="n">
-        <v>12969</v>
+        <v>9640</v>
       </c>
       <c r="D3" t="n">
-        <v>17389</v>
+        <v>24772</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1712</v>
+        <v>2093</v>
       </c>
       <c r="C4" t="n">
-        <v>9835</v>
+        <v>7655</v>
       </c>
       <c r="D4" t="n">
-        <v>7164</v>
+        <v>10758</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1172</v>
+        <v>1499</v>
       </c>
       <c r="C5" t="n">
-        <v>5169</v>
+        <v>3562</v>
       </c>
       <c r="D5" t="n">
-        <v>2263</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>636</v>
+        <v>868</v>
       </c>
       <c r="C6" t="n">
-        <v>3838</v>
+        <v>2544</v>
       </c>
       <c r="D6" t="n">
-        <v>746</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>404</v>
       </c>
       <c r="C7" t="n">
-        <v>2251</v>
+        <v>1525</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="C8" t="n">
-        <v>1040</v>
+        <v>748</v>
       </c>
       <c r="D8" t="n">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>423</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1839,7 +1839,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3689</v>
+        <v>5040</v>
       </c>
       <c r="C2" t="n">
-        <v>3053</v>
+        <v>5029</v>
       </c>
       <c r="D2" t="n">
-        <v>21640</v>
+        <v>32879</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4239</v>
+        <v>5910</v>
       </c>
       <c r="C3" t="n">
-        <v>9035</v>
+        <v>9184</v>
       </c>
       <c r="D3" t="n">
-        <v>17959</v>
+        <v>26773</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2256</v>
+        <v>2989</v>
       </c>
       <c r="C4" t="n">
-        <v>11392</v>
+        <v>8685</v>
       </c>
       <c r="D4" t="n">
-        <v>8556</v>
+        <v>12655</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1288</v>
+        <v>1646</v>
       </c>
       <c r="C5" t="n">
-        <v>7051</v>
+        <v>5269</v>
       </c>
       <c r="D5" t="n">
-        <v>2802</v>
+        <v>3968</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>751</v>
+        <v>1016</v>
       </c>
       <c r="C6" t="n">
-        <v>4508</v>
+        <v>3007</v>
       </c>
       <c r="D6" t="n">
-        <v>890</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>375</v>
       </c>
       <c r="C7" t="n">
-        <v>2815</v>
+        <v>1918</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>1377</v>
+        <v>973</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>383</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
         <v>208</v>
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4303</v>
+        <v>5847</v>
       </c>
       <c r="C2" t="n">
-        <v>4914</v>
+        <v>4763</v>
       </c>
       <c r="D2" t="n">
-        <v>18142</v>
+        <v>32793</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3383</v>
+        <v>4674</v>
       </c>
       <c r="C3" t="n">
-        <v>5620</v>
+        <v>6508</v>
       </c>
       <c r="D3" t="n">
-        <v>17425</v>
+        <v>25804</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2619</v>
+        <v>3618</v>
       </c>
       <c r="C4" t="n">
-        <v>10155</v>
+        <v>8739</v>
       </c>
       <c r="D4" t="n">
-        <v>9740</v>
+        <v>14574</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1496</v>
+        <v>1946</v>
       </c>
       <c r="C5" t="n">
-        <v>8821</v>
+        <v>6700</v>
       </c>
       <c r="D5" t="n">
-        <v>3518</v>
+        <v>5181</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>883</v>
+        <v>1164</v>
       </c>
       <c r="C6" t="n">
-        <v>5540</v>
+        <v>3985</v>
       </c>
       <c r="D6" t="n">
-        <v>1153</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>392</v>
+        <v>543</v>
       </c>
       <c r="C7" t="n">
-        <v>3538</v>
+        <v>2365</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>1939</v>
+        <v>1352</v>
       </c>
       <c r="D8" t="n">
-        <v>344</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>781</v>
+        <v>604</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
         <v>168</v>
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2509,7 +2509,7 @@
         <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2585</v>
+        <v>3559</v>
       </c>
       <c r="C2" t="n">
-        <v>2442</v>
+        <v>2326</v>
       </c>
       <c r="D2" t="n">
-        <v>12847</v>
+        <v>22904</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3494</v>
+        <v>4767</v>
       </c>
       <c r="C3" t="n">
-        <v>5255</v>
+        <v>5772</v>
       </c>
       <c r="D3" t="n">
-        <v>17131</v>
+        <v>25952</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2852</v>
+        <v>3955</v>
       </c>
       <c r="C4" t="n">
-        <v>9569</v>
+        <v>8710</v>
       </c>
       <c r="D4" t="n">
-        <v>10569</v>
+        <v>15900</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1551</v>
+        <v>2026</v>
       </c>
       <c r="C5" t="n">
-        <v>10500</v>
+        <v>8125</v>
       </c>
       <c r="D5" t="n">
-        <v>3632</v>
+        <v>5465</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>704</v>
+        <v>953</v>
       </c>
       <c r="C6" t="n">
-        <v>6462</v>
+        <v>4677</v>
       </c>
       <c r="D6" t="n">
-        <v>1132</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="C7" t="n">
-        <v>3602</v>
+        <v>2470</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1316</v>
+        <v>976</v>
       </c>
       <c r="D8" t="n">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
         <v>164</v>
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2806,7 +2806,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2534</v>
+        <v>4129</v>
       </c>
       <c r="C2" t="n">
-        <v>11076</v>
+        <v>6382</v>
       </c>
       <c r="D2" t="n">
-        <v>14867</v>
+        <v>19504</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2681</v>
+        <v>3669</v>
       </c>
       <c r="C3" t="n">
-        <v>3611</v>
+        <v>3829</v>
       </c>
       <c r="D3" t="n">
-        <v>15458</v>
+        <v>23859</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2705</v>
+        <v>3726</v>
       </c>
       <c r="C4" t="n">
-        <v>7515</v>
+        <v>7203</v>
       </c>
       <c r="D4" t="n">
-        <v>11255</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1829</v>
+        <v>2456</v>
       </c>
       <c r="C5" t="n">
-        <v>9888</v>
+        <v>8286</v>
       </c>
       <c r="D5" t="n">
-        <v>4555</v>
+        <v>6853</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>917</v>
+        <v>1222</v>
       </c>
       <c r="C6" t="n">
-        <v>8159</v>
+        <v>6071</v>
       </c>
       <c r="D6" t="n">
-        <v>1429</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>345</v>
       </c>
       <c r="C7" t="n">
-        <v>4700</v>
+        <v>3360</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>2125</v>
+        <v>1507</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>615</v>
+        <v>490</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>173</v>
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1791</v>
+        <v>2984</v>
       </c>
       <c r="C2" t="n">
-        <v>6632</v>
+        <v>3964</v>
       </c>
       <c r="D2" t="n">
-        <v>10993</v>
+        <v>14166</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2313</v>
+        <v>3340</v>
       </c>
       <c r="C3" t="n">
-        <v>5801</v>
+        <v>4349</v>
       </c>
       <c r="D3" t="n">
-        <v>14575</v>
+        <v>22111</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2483</v>
+        <v>3383</v>
       </c>
       <c r="C4" t="n">
-        <v>6075</v>
+        <v>5965</v>
       </c>
       <c r="D4" t="n">
-        <v>11545</v>
+        <v>17468</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1965</v>
+        <v>2686</v>
       </c>
       <c r="C5" t="n">
-        <v>9264</v>
+        <v>7988</v>
       </c>
       <c r="D5" t="n">
-        <v>5211</v>
+        <v>7843</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1056</v>
+        <v>1410</v>
       </c>
       <c r="C6" t="n">
-        <v>8989</v>
+        <v>6967</v>
       </c>
       <c r="D6" t="n">
-        <v>1680</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>224</v>
+        <v>306</v>
       </c>
       <c r="C7" t="n">
-        <v>5720</v>
+        <v>4200</v>
       </c>
       <c r="D7" t="n">
-        <v>691</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>2727</v>
+        <v>1922</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>652</v>
+        <v>544</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3400,7 +3400,7 @@
         <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2830</v>
+        <v>3595</v>
       </c>
       <c r="C2" t="n">
-        <v>7500</v>
+        <v>6854</v>
       </c>
       <c r="D2" t="n">
-        <v>11880</v>
+        <v>12433</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1802</v>
+        <v>2713</v>
       </c>
       <c r="C3" t="n">
-        <v>5514</v>
+        <v>3753</v>
       </c>
       <c r="D3" t="n">
-        <v>13264</v>
+        <v>19841</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2129</v>
+        <v>2927</v>
       </c>
       <c r="C4" t="n">
-        <v>5782</v>
+        <v>5189</v>
       </c>
       <c r="D4" t="n">
-        <v>11601</v>
+        <v>17560</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1944</v>
+        <v>2684</v>
       </c>
       <c r="C5" t="n">
-        <v>7846</v>
+        <v>7045</v>
       </c>
       <c r="D5" t="n">
-        <v>5843</v>
+        <v>8730</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1248</v>
+        <v>1670</v>
       </c>
       <c r="C6" t="n">
-        <v>9017</v>
+        <v>7283</v>
       </c>
       <c r="D6" t="n">
-        <v>2049</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>413</v>
+        <v>569</v>
       </c>
       <c r="C7" t="n">
-        <v>6927</v>
+        <v>5174</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>3693</v>
+        <v>2699</v>
       </c>
       <c r="D8" t="n">
-        <v>425</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1288</v>
+        <v>962</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5024</v>
+        <v>8558</v>
       </c>
       <c r="C2" t="n">
-        <v>9822</v>
+        <v>6637</v>
       </c>
       <c r="D2" t="n">
-        <v>11612</v>
+        <v>15041</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2089</v>
+        <v>2631</v>
       </c>
       <c r="C2" t="n">
-        <v>4440</v>
+        <v>4057</v>
       </c>
       <c r="D2" t="n">
-        <v>8838</v>
+        <v>9250</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2441</v>
+        <v>3542</v>
       </c>
       <c r="C3" t="n">
-        <v>6540</v>
+        <v>4790</v>
       </c>
       <c r="D3" t="n">
-        <v>14289</v>
+        <v>21092</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2866</v>
+        <v>3976</v>
       </c>
       <c r="C4" t="n">
-        <v>8499</v>
+        <v>7519</v>
       </c>
       <c r="D4" t="n">
-        <v>11704</v>
+        <v>17604</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1171</v>
+        <v>1567</v>
       </c>
       <c r="C5" t="n">
-        <v>12230</v>
+        <v>10316</v>
       </c>
       <c r="D5" t="n">
-        <v>5174</v>
+        <v>7760</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>381</v>
+        <v>525</v>
       </c>
       <c r="C6" t="n">
-        <v>8290</v>
+        <v>6355</v>
       </c>
       <c r="D6" t="n">
-        <v>1673</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>3619</v>
+        <v>2645</v>
       </c>
       <c r="D7" t="n">
-        <v>510</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1262</v>
+        <v>942</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>35</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6003</v>
+        <v>7466</v>
       </c>
       <c r="C2" t="n">
-        <v>9147</v>
+        <v>5596</v>
       </c>
       <c r="D2" t="n">
-        <v>13760</v>
+        <v>25669</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2135</v>
+        <v>3634</v>
       </c>
       <c r="C3" t="n">
-        <v>4950</v>
+        <v>3345</v>
       </c>
       <c r="D3" t="n">
-        <v>2590</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4357</v>
+        <v>6121</v>
       </c>
       <c r="C2" t="n">
-        <v>9962</v>
+        <v>7608</v>
       </c>
       <c r="D2" t="n">
-        <v>18388</v>
+        <v>25345</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3340</v>
+        <v>4563</v>
       </c>
       <c r="C3" t="n">
-        <v>6317</v>
+        <v>3983</v>
       </c>
       <c r="D3" t="n">
-        <v>4275</v>
+        <v>6713</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>962</v>
+        <v>1613</v>
       </c>
       <c r="C4" t="n">
-        <v>2944</v>
+        <v>2004</v>
       </c>
       <c r="D4" t="n">
-        <v>1703</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5494</v>
+        <v>6738</v>
       </c>
       <c r="C2" t="n">
-        <v>11850</v>
+        <v>6450</v>
       </c>
       <c r="D2" t="n">
-        <v>15991</v>
+        <v>28125</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3159</v>
+        <v>4382</v>
       </c>
       <c r="C3" t="n">
-        <v>7249</v>
+        <v>5136</v>
       </c>
       <c r="D3" t="n">
-        <v>6225</v>
+        <v>9210</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1828</v>
+        <v>2633</v>
       </c>
       <c r="C4" t="n">
-        <v>4732</v>
+        <v>3044</v>
       </c>
       <c r="D4" t="n">
-        <v>2145</v>
+        <v>2703</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>447</v>
+        <v>708</v>
       </c>
       <c r="C5" t="n">
-        <v>1705</v>
+        <v>1193</v>
       </c>
       <c r="D5" t="n">
-        <v>1242</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5020</v>
+        <v>6638</v>
       </c>
       <c r="C2" t="n">
-        <v>6453</v>
+        <v>5078</v>
       </c>
       <c r="D2" t="n">
-        <v>16303</v>
+        <v>30999</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3475</v>
+        <v>4495</v>
       </c>
       <c r="C3" t="n">
-        <v>8345</v>
+        <v>5056</v>
       </c>
       <c r="D3" t="n">
-        <v>7271</v>
+        <v>11436</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2094</v>
+        <v>2951</v>
       </c>
       <c r="C4" t="n">
-        <v>5917</v>
+        <v>4056</v>
       </c>
       <c r="D4" t="n">
-        <v>2823</v>
+        <v>3807</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>936</v>
+        <v>1382</v>
       </c>
       <c r="C5" t="n">
-        <v>3238</v>
+        <v>2127</v>
       </c>
       <c r="D5" t="n">
-        <v>1348</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>1000</v>
+        <v>745</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,7 +5543,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
         <v>306</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6837</v>
+        <v>6561</v>
       </c>
       <c r="C2" t="n">
-        <v>11492</v>
+        <v>6431</v>
       </c>
       <c r="D2" t="n">
-        <v>26903</v>
+        <v>34589</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3059</v>
+        <v>4005</v>
       </c>
       <c r="C3" t="n">
-        <v>6064</v>
+        <v>4154</v>
       </c>
       <c r="D3" t="n">
-        <v>7651</v>
+        <v>12799</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1703</v>
+        <v>2280</v>
       </c>
       <c r="C4" t="n">
-        <v>5872</v>
+        <v>3761</v>
       </c>
       <c r="D4" t="n">
-        <v>3094</v>
+        <v>4435</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>783</v>
+        <v>1123</v>
       </c>
       <c r="C5" t="n">
-        <v>3380</v>
+        <v>2254</v>
       </c>
       <c r="D5" t="n">
-        <v>1254</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>281</v>
+        <v>410</v>
       </c>
       <c r="C6" t="n">
-        <v>1417</v>
+        <v>961</v>
       </c>
       <c r="D6" t="n">
-        <v>776</v>
+        <v>793</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>420</v>
+        <v>343</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4920</v>
+        <v>6171</v>
       </c>
       <c r="C2" t="n">
-        <v>7973</v>
+        <v>10840</v>
       </c>
       <c r="D2" t="n">
-        <v>22688</v>
+        <v>30120</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4095</v>
+        <v>4367</v>
       </c>
       <c r="C3" t="n">
-        <v>7912</v>
+        <v>4705</v>
       </c>
       <c r="D3" t="n">
-        <v>10322</v>
+        <v>15517</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2080</v>
+        <v>2745</v>
       </c>
       <c r="C4" t="n">
-        <v>5864</v>
+        <v>3916</v>
       </c>
       <c r="D4" t="n">
-        <v>3918</v>
+        <v>5986</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1094</v>
+        <v>1500</v>
       </c>
       <c r="C5" t="n">
-        <v>4745</v>
+        <v>3053</v>
       </c>
       <c r="D5" t="n">
-        <v>1557</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>492</v>
+        <v>709</v>
       </c>
       <c r="C6" t="n">
-        <v>2479</v>
+        <v>1681</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="C7" t="n">
-        <v>976</v>
+        <v>688</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>131</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3699</v>
+        <v>6022</v>
       </c>
       <c r="C2" t="n">
-        <v>8531</v>
+        <v>7254</v>
       </c>
       <c r="D2" t="n">
-        <v>29481</v>
+        <v>40538</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3703</v>
+        <v>4304</v>
       </c>
       <c r="C3" t="n">
-        <v>6901</v>
+        <v>6926</v>
       </c>
       <c r="D3" t="n">
-        <v>11474</v>
+        <v>16736</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2631</v>
+        <v>3025</v>
       </c>
       <c r="C4" t="n">
-        <v>6806</v>
+        <v>4273</v>
       </c>
       <c r="D4" t="n">
-        <v>4929</v>
+        <v>7633</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1371</v>
+        <v>1861</v>
       </c>
       <c r="C5" t="n">
-        <v>5247</v>
+        <v>3453</v>
       </c>
       <c r="D5" t="n">
-        <v>1940</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>714</v>
+        <v>990</v>
       </c>
       <c r="C6" t="n">
-        <v>3625</v>
+        <v>2356</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>412</v>
       </c>
       <c r="C7" t="n">
-        <v>1741</v>
+        <v>1203</v>
       </c>
       <c r="D7" t="n">
-        <v>604</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>642</v>
+        <v>487</v>
       </c>
       <c r="D8" t="n">
         <v>404</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">

--- a/output/yearly_population_iteration_41_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_41_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8304</v>
+        <v>1164</v>
       </c>
       <c r="C2" t="n">
-        <v>7192</v>
+        <v>4093</v>
       </c>
       <c r="D2" t="n">
-        <v>45881</v>
+        <v>12096</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4173</v>
+        <v>1852</v>
       </c>
       <c r="C3" t="n">
-        <v>6200</v>
+        <v>9264</v>
       </c>
       <c r="D3" t="n">
-        <v>19012</v>
+        <v>12900</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3082</v>
+        <v>1179</v>
       </c>
       <c r="C4" t="n">
-        <v>5533</v>
+        <v>9923</v>
       </c>
       <c r="D4" t="n">
-        <v>8973</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2122</v>
+        <v>614</v>
       </c>
       <c r="C5" t="n">
-        <v>3749</v>
+        <v>5058</v>
       </c>
       <c r="D5" t="n">
-        <v>3354</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1253</v>
+        <v>251</v>
       </c>
       <c r="C6" t="n">
-        <v>2858</v>
+        <v>1864</v>
       </c>
       <c r="D6" t="n">
-        <v>1314</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>598</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1733</v>
+        <v>695</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>816</v>
+        <v>349</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>351</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8216</v>
+        <v>1677</v>
       </c>
       <c r="C2" t="n">
-        <v>7817</v>
+        <v>5477</v>
       </c>
       <c r="D2" t="n">
-        <v>50067</v>
+        <v>17051</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4790</v>
+        <v>1289</v>
       </c>
       <c r="C3" t="n">
-        <v>5856</v>
+        <v>5779</v>
       </c>
       <c r="D3" t="n">
-        <v>21204</v>
+        <v>11869</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3023</v>
+        <v>1298</v>
       </c>
       <c r="C4" t="n">
-        <v>5672</v>
+        <v>9362</v>
       </c>
       <c r="D4" t="n">
-        <v>10156</v>
+        <v>7361</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2239</v>
+        <v>772</v>
       </c>
       <c r="C5" t="n">
-        <v>4475</v>
+        <v>7523</v>
       </c>
       <c r="D5" t="n">
-        <v>4115</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1486</v>
+        <v>375</v>
       </c>
       <c r="C6" t="n">
-        <v>3188</v>
+        <v>3426</v>
       </c>
       <c r="D6" t="n">
-        <v>1577</v>
+        <v>969</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>775</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>2217</v>
+        <v>1251</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1185</v>
+        <v>504</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>534</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8922</v>
+        <v>900</v>
       </c>
       <c r="C2" t="n">
-        <v>15372</v>
+        <v>2307</v>
       </c>
       <c r="D2" t="n">
-        <v>58888</v>
+        <v>11643</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5043</v>
+        <v>1343</v>
       </c>
       <c r="C3" t="n">
-        <v>5899</v>
+        <v>5431</v>
       </c>
       <c r="D3" t="n">
-        <v>23310</v>
+        <v>12186</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3143</v>
+        <v>1417</v>
       </c>
       <c r="C4" t="n">
-        <v>5631</v>
+        <v>8780</v>
       </c>
       <c r="D4" t="n">
-        <v>11438</v>
+        <v>7966</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2266</v>
+        <v>779</v>
       </c>
       <c r="C5" t="n">
-        <v>4821</v>
+        <v>8960</v>
       </c>
       <c r="D5" t="n">
-        <v>4762</v>
+        <v>3094</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1623</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>3635</v>
+        <v>4389</v>
       </c>
       <c r="D6" t="n">
-        <v>1882</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>940</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2596</v>
+        <v>1203</v>
       </c>
       <c r="D7" t="n">
-        <v>864</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1557</v>
+        <v>481</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>764</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>355</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8307</v>
+        <v>763</v>
       </c>
       <c r="C2" t="n">
-        <v>10698</v>
+        <v>5455</v>
       </c>
       <c r="D2" t="n">
-        <v>48229</v>
+        <v>11096</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5814</v>
+        <v>976</v>
       </c>
       <c r="C3" t="n">
-        <v>9640</v>
+        <v>3413</v>
       </c>
       <c r="D3" t="n">
-        <v>24772</v>
+        <v>11269</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2093</v>
+        <v>1228</v>
       </c>
       <c r="C4" t="n">
-        <v>7655</v>
+        <v>6945</v>
       </c>
       <c r="D4" t="n">
-        <v>10758</v>
+        <v>8453</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1499</v>
+        <v>938</v>
       </c>
       <c r="C5" t="n">
-        <v>3562</v>
+        <v>8771</v>
       </c>
       <c r="D5" t="n">
-        <v>3124</v>
+        <v>3795</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>868</v>
+        <v>445</v>
       </c>
       <c r="C6" t="n">
-        <v>2544</v>
+        <v>6537</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>404</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>1525</v>
+        <v>2599</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>748</v>
+        <v>773</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5040</v>
+        <v>421</v>
       </c>
       <c r="C2" t="n">
-        <v>5029</v>
+        <v>3608</v>
       </c>
       <c r="D2" t="n">
-        <v>32879</v>
+        <v>8049</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5910</v>
+        <v>786</v>
       </c>
       <c r="C3" t="n">
-        <v>9184</v>
+        <v>3874</v>
       </c>
       <c r="D3" t="n">
-        <v>26773</v>
+        <v>10615</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2989</v>
+        <v>1056</v>
       </c>
       <c r="C4" t="n">
-        <v>8685</v>
+        <v>5406</v>
       </c>
       <c r="D4" t="n">
-        <v>12655</v>
+        <v>8682</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1646</v>
+        <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>5269</v>
+        <v>8189</v>
       </c>
       <c r="D5" t="n">
-        <v>3968</v>
+        <v>4333</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1016</v>
+        <v>539</v>
       </c>
       <c r="C6" t="n">
-        <v>3007</v>
+        <v>7579</v>
       </c>
       <c r="D6" t="n">
-        <v>1057</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>375</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>1918</v>
+        <v>3895</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>973</v>
+        <v>1209</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5847</v>
+        <v>842</v>
       </c>
       <c r="C2" t="n">
-        <v>4763</v>
+        <v>9595</v>
       </c>
       <c r="D2" t="n">
-        <v>32793</v>
+        <v>12041</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4674</v>
+        <v>539</v>
       </c>
       <c r="C3" t="n">
-        <v>6508</v>
+        <v>3311</v>
       </c>
       <c r="D3" t="n">
-        <v>25804</v>
+        <v>9654</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3618</v>
+        <v>834</v>
       </c>
       <c r="C4" t="n">
-        <v>8739</v>
+        <v>4572</v>
       </c>
       <c r="D4" t="n">
-        <v>14574</v>
+        <v>8631</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1946</v>
+        <v>942</v>
       </c>
       <c r="C5" t="n">
-        <v>6700</v>
+        <v>6841</v>
       </c>
       <c r="D5" t="n">
-        <v>5181</v>
+        <v>4869</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1164</v>
+        <v>657</v>
       </c>
       <c r="C6" t="n">
-        <v>3985</v>
+        <v>7766</v>
       </c>
       <c r="D6" t="n">
-        <v>1462</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>543</v>
+        <v>250</v>
       </c>
       <c r="C7" t="n">
-        <v>2365</v>
+        <v>5447</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1352</v>
+        <v>2246</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>604</v>
+        <v>700</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3559</v>
+        <v>579</v>
       </c>
       <c r="C2" t="n">
-        <v>2326</v>
+        <v>5143</v>
       </c>
       <c r="D2" t="n">
-        <v>22904</v>
+        <v>8765</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4767</v>
+        <v>795</v>
       </c>
       <c r="C3" t="n">
-        <v>5772</v>
+        <v>5234</v>
       </c>
       <c r="D3" t="n">
-        <v>25952</v>
+        <v>10631</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3955</v>
+        <v>1287</v>
       </c>
       <c r="C4" t="n">
-        <v>8710</v>
+        <v>6770</v>
       </c>
       <c r="D4" t="n">
-        <v>15900</v>
+        <v>8863</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2026</v>
+        <v>659</v>
       </c>
       <c r="C5" t="n">
-        <v>8125</v>
+        <v>10446</v>
       </c>
       <c r="D5" t="n">
-        <v>5465</v>
+        <v>4525</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>953</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>4677</v>
+        <v>7164</v>
       </c>
       <c r="D6" t="n">
-        <v>1404</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>2470</v>
+        <v>2201</v>
       </c>
       <c r="D7" t="n">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>976</v>
+        <v>686</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4129</v>
+        <v>350</v>
       </c>
       <c r="C2" t="n">
-        <v>6382</v>
+        <v>3272</v>
       </c>
       <c r="D2" t="n">
-        <v>19504</v>
+        <v>6334</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3669</v>
+        <v>595</v>
       </c>
       <c r="C3" t="n">
-        <v>3829</v>
+        <v>4578</v>
       </c>
       <c r="D3" t="n">
-        <v>23859</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3726</v>
+        <v>884</v>
       </c>
       <c r="C4" t="n">
-        <v>7203</v>
+        <v>5688</v>
       </c>
       <c r="D4" t="n">
-        <v>16960</v>
+        <v>8613</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2456</v>
+        <v>646</v>
       </c>
       <c r="C5" t="n">
-        <v>8286</v>
+        <v>7768</v>
       </c>
       <c r="D5" t="n">
-        <v>6853</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1222</v>
+        <v>229</v>
       </c>
       <c r="C6" t="n">
-        <v>6071</v>
+        <v>6997</v>
       </c>
       <c r="D6" t="n">
-        <v>1892</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>3360</v>
+        <v>3045</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1507</v>
+        <v>812</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>490</v>
+        <v>262</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>123</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2984</v>
+        <v>198</v>
       </c>
       <c r="C2" t="n">
-        <v>3964</v>
+        <v>9109</v>
       </c>
       <c r="D2" t="n">
-        <v>14166</v>
+        <v>6741</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3340</v>
+        <v>400</v>
       </c>
       <c r="C3" t="n">
-        <v>4349</v>
+        <v>3381</v>
       </c>
       <c r="D3" t="n">
-        <v>22111</v>
+        <v>8427</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3383</v>
+        <v>660</v>
       </c>
       <c r="C4" t="n">
-        <v>5965</v>
+        <v>4962</v>
       </c>
       <c r="D4" t="n">
-        <v>17468</v>
+        <v>8531</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2686</v>
+        <v>683</v>
       </c>
       <c r="C5" t="n">
-        <v>7988</v>
+        <v>6582</v>
       </c>
       <c r="D5" t="n">
-        <v>7843</v>
+        <v>5116</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1410</v>
+        <v>375</v>
       </c>
       <c r="C6" t="n">
-        <v>6967</v>
+        <v>7306</v>
       </c>
       <c r="D6" t="n">
-        <v>2287</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>4200</v>
+        <v>5010</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>750</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1922</v>
+        <v>1848</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>544</v>
+        <v>501</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3595</v>
+        <v>306</v>
       </c>
       <c r="C2" t="n">
-        <v>6854</v>
+        <v>19631</v>
       </c>
       <c r="D2" t="n">
-        <v>12433</v>
+        <v>7465</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2713</v>
+        <v>262</v>
       </c>
       <c r="C3" t="n">
-        <v>3753</v>
+        <v>5347</v>
       </c>
       <c r="D3" t="n">
-        <v>19841</v>
+        <v>7604</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2927</v>
+        <v>478</v>
       </c>
       <c r="C4" t="n">
-        <v>5189</v>
+        <v>4069</v>
       </c>
       <c r="D4" t="n">
-        <v>17560</v>
+        <v>8253</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2684</v>
+        <v>609</v>
       </c>
       <c r="C5" t="n">
-        <v>7045</v>
+        <v>5667</v>
       </c>
       <c r="D5" t="n">
-        <v>8730</v>
+        <v>5517</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1670</v>
+        <v>467</v>
       </c>
       <c r="C6" t="n">
-        <v>7283</v>
+        <v>6827</v>
       </c>
       <c r="D6" t="n">
-        <v>2951</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>569</v>
+        <v>198</v>
       </c>
       <c r="C7" t="n">
-        <v>5174</v>
+        <v>6065</v>
       </c>
       <c r="D7" t="n">
-        <v>931</v>
+        <v>962</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>2699</v>
+        <v>3241</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>962</v>
+        <v>1068</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8558</v>
+        <v>2969</v>
       </c>
       <c r="C2" t="n">
-        <v>6637</v>
+        <v>9987</v>
       </c>
       <c r="D2" t="n">
-        <v>15041</v>
+        <v>18229</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2631</v>
+        <v>177</v>
       </c>
       <c r="C2" t="n">
-        <v>4057</v>
+        <v>24951</v>
       </c>
       <c r="D2" t="n">
-        <v>9250</v>
+        <v>14009</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3542</v>
+        <v>231</v>
       </c>
       <c r="C3" t="n">
-        <v>4790</v>
+        <v>10101</v>
       </c>
       <c r="D3" t="n">
-        <v>21092</v>
+        <v>7087</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3976</v>
+        <v>343</v>
       </c>
       <c r="C4" t="n">
-        <v>7519</v>
+        <v>4560</v>
       </c>
       <c r="D4" t="n">
-        <v>17604</v>
+        <v>7902</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1567</v>
+        <v>510</v>
       </c>
       <c r="C5" t="n">
-        <v>10316</v>
+        <v>4804</v>
       </c>
       <c r="D5" t="n">
-        <v>7760</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>525</v>
+        <v>483</v>
       </c>
       <c r="C6" t="n">
-        <v>6355</v>
+        <v>6274</v>
       </c>
       <c r="D6" t="n">
-        <v>2219</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>2645</v>
+        <v>6376</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>942</v>
+        <v>4314</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>1898</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>580</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7466</v>
+        <v>5221</v>
       </c>
       <c r="C2" t="n">
-        <v>5596</v>
+        <v>7797</v>
       </c>
       <c r="D2" t="n">
-        <v>25669</v>
+        <v>23364</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3634</v>
+        <v>960</v>
       </c>
       <c r="C3" t="n">
-        <v>3345</v>
+        <v>3943</v>
       </c>
       <c r="D3" t="n">
-        <v>3166</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6121</v>
+        <v>2510</v>
       </c>
       <c r="C2" t="n">
-        <v>7608</v>
+        <v>7551</v>
       </c>
       <c r="D2" t="n">
-        <v>25345</v>
+        <v>17110</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4563</v>
+        <v>2631</v>
       </c>
       <c r="C3" t="n">
-        <v>3983</v>
+        <v>5379</v>
       </c>
       <c r="D3" t="n">
-        <v>6713</v>
+        <v>6428</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1613</v>
+        <v>471</v>
       </c>
       <c r="C4" t="n">
-        <v>2004</v>
+        <v>2508</v>
       </c>
       <c r="D4" t="n">
-        <v>1819</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6738</v>
+        <v>1627</v>
       </c>
       <c r="C2" t="n">
-        <v>6450</v>
+        <v>7613</v>
       </c>
       <c r="D2" t="n">
-        <v>28125</v>
+        <v>24229</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4382</v>
+        <v>2120</v>
       </c>
       <c r="C3" t="n">
-        <v>5136</v>
+        <v>5707</v>
       </c>
       <c r="D3" t="n">
-        <v>9210</v>
+        <v>7749</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2633</v>
+        <v>1366</v>
       </c>
       <c r="C4" t="n">
-        <v>3044</v>
+        <v>4164</v>
       </c>
       <c r="D4" t="n">
-        <v>2703</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>708</v>
+        <v>248</v>
       </c>
       <c r="C5" t="n">
-        <v>1193</v>
+        <v>1529</v>
       </c>
       <c r="D5" t="n">
-        <v>1263</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6638</v>
+        <v>1546</v>
       </c>
       <c r="C2" t="n">
-        <v>5078</v>
+        <v>7071</v>
       </c>
       <c r="D2" t="n">
-        <v>30999</v>
+        <v>22413</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4495</v>
+        <v>1558</v>
       </c>
       <c r="C3" t="n">
-        <v>5056</v>
+        <v>5839</v>
       </c>
       <c r="D3" t="n">
-        <v>11436</v>
+        <v>9827</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2951</v>
+        <v>1490</v>
       </c>
       <c r="C4" t="n">
-        <v>4056</v>
+        <v>4951</v>
       </c>
       <c r="D4" t="n">
-        <v>3807</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1382</v>
+        <v>682</v>
       </c>
       <c r="C5" t="n">
-        <v>2127</v>
+        <v>2939</v>
       </c>
       <c r="D5" t="n">
-        <v>1461</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>360</v>
+        <v>162</v>
       </c>
       <c r="C6" t="n">
-        <v>745</v>
+        <v>928</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6561</v>
+        <v>2320</v>
       </c>
       <c r="C2" t="n">
-        <v>6431</v>
+        <v>12512</v>
       </c>
       <c r="D2" t="n">
-        <v>34589</v>
+        <v>18852</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4005</v>
+        <v>1284</v>
       </c>
       <c r="C3" t="n">
-        <v>4154</v>
+        <v>5634</v>
       </c>
       <c r="D3" t="n">
-        <v>12799</v>
+        <v>11048</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2280</v>
+        <v>1322</v>
       </c>
       <c r="C4" t="n">
-        <v>3761</v>
+        <v>5325</v>
       </c>
       <c r="D4" t="n">
-        <v>4435</v>
+        <v>4578</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1123</v>
+        <v>930</v>
       </c>
       <c r="C5" t="n">
-        <v>2254</v>
+        <v>3920</v>
       </c>
       <c r="D5" t="n">
-        <v>1464</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>410</v>
+        <v>357</v>
       </c>
       <c r="C6" t="n">
-        <v>961</v>
+        <v>1912</v>
       </c>
       <c r="D6" t="n">
-        <v>793</v>
+        <v>923</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="C7" t="n">
-        <v>343</v>
+        <v>611</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>299</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6171</v>
+        <v>2629</v>
       </c>
       <c r="C2" t="n">
-        <v>10840</v>
+        <v>14032</v>
       </c>
       <c r="D2" t="n">
-        <v>30120</v>
+        <v>22482</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4367</v>
+        <v>1429</v>
       </c>
       <c r="C3" t="n">
-        <v>4705</v>
+        <v>7901</v>
       </c>
       <c r="D3" t="n">
-        <v>15517</v>
+        <v>11411</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2745</v>
+        <v>1134</v>
       </c>
       <c r="C4" t="n">
-        <v>3916</v>
+        <v>5317</v>
       </c>
       <c r="D4" t="n">
-        <v>5986</v>
+        <v>5556</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1500</v>
+        <v>980</v>
       </c>
       <c r="C5" t="n">
-        <v>3053</v>
+        <v>4526</v>
       </c>
       <c r="D5" t="n">
-        <v>1975</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>709</v>
+        <v>553</v>
       </c>
       <c r="C6" t="n">
-        <v>1681</v>
+        <v>2837</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="C7" t="n">
-        <v>688</v>
+        <v>1204</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>287</v>
+        <v>439</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>238</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6022</v>
+        <v>2334</v>
       </c>
       <c r="C2" t="n">
-        <v>7254</v>
+        <v>8755</v>
       </c>
       <c r="D2" t="n">
-        <v>40538</v>
+        <v>17665</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4304</v>
+        <v>1952</v>
       </c>
       <c r="C3" t="n">
-        <v>6926</v>
+        <v>11841</v>
       </c>
       <c r="D3" t="n">
-        <v>16736</v>
+        <v>12821</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3025</v>
+        <v>905</v>
       </c>
       <c r="C4" t="n">
-        <v>4273</v>
+        <v>7662</v>
       </c>
       <c r="D4" t="n">
-        <v>7633</v>
+        <v>5172</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1861</v>
+        <v>510</v>
       </c>
       <c r="C5" t="n">
-        <v>3453</v>
+        <v>2780</v>
       </c>
       <c r="D5" t="n">
-        <v>2646</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>990</v>
+        <v>182</v>
       </c>
       <c r="C6" t="n">
-        <v>2356</v>
+        <v>1179</v>
       </c>
       <c r="D6" t="n">
-        <v>1072</v>
+        <v>648</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>1203</v>
+        <v>430</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>487</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
         <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
